--- a/apps/cash-confidence/Cool_Hollow_Coaching_Milestone_5_Cash_Confidence_Template.xlsx
+++ b/apps/cash-confidence/Cool_Hollow_Coaching_Milestone_5_Cash_Confidence_Template.xlsx
@@ -37,17 +37,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00E8C766"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
     <font>
@@ -58,7 +58,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -76,11 +76,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <i val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -89,12 +89,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E4643"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00589BA8"/>
+        <fgColor rgb="001A1A1A"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,12 +99,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B4D351"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,19 +146,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/apps/cash-confidence/Cool_Hollow_Coaching_Milestone_5_Cash_Confidence_Template.xlsx
+++ b/apps/cash-confidence/Cool_Hollow_Coaching_Milestone_5_Cash_Confidence_Template.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Items" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Recurring Expenses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Receivables Aging" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Examples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Starter Ideas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recurring Expenses" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Receivables Aging" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,12 +45,32 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
@@ -63,21 +87,8 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="005A5A5A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
       <color rgb="006B6B6B"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -94,12 +105,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8C766"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,11 +145,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -146,19 +158,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,10 +544,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001A1A1A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -537,245 +561,304 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 5: Cash Confidence</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>How to use this template</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>This template has three tabs. Fill in your 13-week cash items (every inflow and outflow you can see coming) on the first tab. Fill in your recurring expenses, rated against the five Decision Filter questions, on the second tab. The third tab is optional: list any customer currently paying late against your own terms, since that's usually a bigger cash lever than any expense you could cut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Three data tabs. Cash Items: every inflow and outflow you can see coming over the next 13 weeks. Recurring Expenses: each recurring expense rated against the five Decision Filter questions. Receivables Aging (optional): any customer paying late against your own terms. Then upload this same file into each upload box in the tool, each box automatically reads the tab it needs. The Starter Ideas tab lists the cash items owners most often forget, worth a scan before you call the list complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Three steps: fill in the data tab(s), save this file, then upload this same file into the tool. The Examples and Starter Ideas tabs are for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads them, only type your real data on the data tab(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>On the "Cash Items" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>What to put here</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>A whole number from 1 to 13.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>inflow or outflow.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>A short label. If this row is a recurring expense you've also rated on the Recurring Expenses tab, use that exact expense name here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>A short label. If this row is a recurring expense you've also rated on the Recurring Expenses tab, use that exact expense name here so the two match up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Optional detail.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>A positive dollar amount.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>On the "Recurring Expenses" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>What to put here</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Expense Name</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Must match the Category or Description used for this expense on the Cash Items tab.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Weekly Amount</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>The weekly cost of this recurring expense.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Core Customer Fit</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>1 to 5. Does this expense serve your core customer?</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Revenue Risk If Cut</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>1 to 5. Would cutting this put revenue at risk in the next 90 days?</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Roi Clarity</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>ROI Clarity</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>1 to 5. Is there a clear, measurable return on this spend?</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>No Cheaper Alternative</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>1 to 5. Is there no cheaper way to get the same outcome?</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Would Approve Today</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>1 to 5. If you were signing this contract fresh today, would you?</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>On the "Receivables Aging" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>What to put here</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Optional tab, but usually the bigger lever than cutting any expense. One row per customer who owes you money.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Optional tab, but usually a bigger cash lever than cutting any expense. One row per customer who owes you money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Amount Outstanding</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>The total dollar amount this customer currently owes you.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Terms Days</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>What your stated payment terms are, e.g. net-30 is 30.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Days Outstanding</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>How long the invoice has actually been unpaid, in days.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Fill in the data tab, save the file, then upload it straight into the tool.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="8">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -784,10 +867,527 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B6B6B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 5: Cash Confidence</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Filled-in examples, for reference only. Type your own data on the data tab(s), not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, anything you type here is ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Cash Items" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>inflow</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>client revenue</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Recurring client payments</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>outflow</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Biweekly payroll</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>outflow</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>rent</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Office lease</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Recurring Expenses" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Expense Name</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Weekly Amount</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Core Customer Fit</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Revenue Risk If Cut</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>ROI Clarity</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>No Cheaper Alternative</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Would Approve Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Underused software bundle</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Receivables Aging" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Amount Outstanding</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Terms Days</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Days Outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Big Client Co</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Steady Client</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8C766"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 5: Cash Confidence</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>The cash items owners most often forget, which is exactly how a 13-week forecast ends up looking calmer than the 13 weeks ahead of you. Scan this before you call your list complete, add anything that applies with your own real amounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, copy items onto the data tab to use them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Outflows that get forgotten</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Quarterly tax payments</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Insurance premiums (annual or semi-annual renewals)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Loan and equipment finance payments</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Credit card payments</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Software subscriptions (annual renewals especially)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Vehicle costs: fuel, maintenance, registration</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Merchant and payment processing fees</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Owner draw or distributions</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Seasonal inventory or materials stock-up</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Marketing and advertising spend</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Inflows worth listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Recurring client payments, by actual expected week</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Deposits on newly signed work</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Tax refunds due</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Rebates or vendor credits owed to you</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -803,352 +1403,341 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 5: Cash Confidence</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>inflow</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>client revenue</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>recurring client payments</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>12000</v>
-      </c>
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>outflow</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>biweekly payroll</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="17" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A8:A42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 13." type="whole" operator="between">
+    <dataValidation sqref="A5:A44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 13." promptTitle="Rate 1 to 13" prompt="Which of the 13 weeks this lands in" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>13</formula2>
     </dataValidation>
-    <dataValidation sqref="B8:B42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: inflow, outflow" type="list">
+    <dataValidation sqref="B5:B44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: inflow, outflow" promptTitle="Pick from the list" prompt="Money coming in, or going out?" type="list">
       <formula1>"inflow,outflow"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1156,13 +1745,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C8A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1180,448 +1770,447 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 5: Cash Confidence</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Expense Name</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Weekly Amount</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Core Customer Fit</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Revenue Risk If Cut</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Roi Clarity</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>ROI Clarity</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>No Cheaper Alternative</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Would Approve Today</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Underused software bundle</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>400</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
+      <c r="A39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
+      <c r="A40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
+      <c r="A41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
+      <c r="A42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="C8:C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Does this expense serve your core customer?" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="D8:D42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Would cutting this risk revenue in the next 90 days?" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="E8:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Is there a clear, measurable return on this spend?" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="F8:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Is there no cheaper way to get the same outcome?" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="G8:G42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="G5:G44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="Signing fresh today, would you approve this?" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -1630,13 +2219,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C8A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1651,290 +2241,286 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 5: Cash Confidence</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Amount Outstanding</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Terms Days</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Days Outstanding</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Big Client Co</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>75</v>
-      </c>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Steady Client</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
+      <c r="A39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
+      <c r="A40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
+      <c r="A41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
+      <c r="A42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
